--- a/ARGX.xlsx
+++ b/ARGX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30949E72-6B57-4A38-9590-B08692D0D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F96FA86-405F-4EC2-854E-D1A8B73BA27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14265" yWindow="1680" windowWidth="14325" windowHeight="11745" activeTab="1" xr2:uid="{0DAA4E62-F5A3-42B7-9991-5143FBFA4FA5}"/>
+    <workbookView xWindow="13160" yWindow="4120" windowWidth="19050" windowHeight="16100" xr2:uid="{0DAA4E62-F5A3-42B7-9991-5143FBFA4FA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
   <si>
     <t>Price</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Upside</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -887,17 +890,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC072C-9090-47FE-AE79-FF8859A46899}">
   <dimension ref="B2:L11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="9" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="9" width="7.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
@@ -916,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>541.65</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="17" t="s">
         <v>6</v>
       </c>
@@ -936,13 +939,13 @@
         <v>1</v>
       </c>
       <c r="K3" s="11">
-        <v>60.1</v>
+        <v>64.409487999999996</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -954,10 +957,10 @@
       </c>
       <c r="K4" s="11">
         <f>+K2*K3</f>
-        <v>32553.165000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>56487.120975999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
@@ -974,13 +977,14 @@
         <v>3</v>
       </c>
       <c r="K5" s="11">
-        <v>3374</v>
+        <f>3587+1600</f>
+        <v>5187</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -998,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
@@ -1017,10 +1021,10 @@
       </c>
       <c r="K7" s="11">
         <f>+K4-K5+K6</f>
-        <v>29179.165000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>51300.120975999998</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>71</v>
       </c>
@@ -1032,7 +1036,7 @@
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>73</v>
       </c>
@@ -1047,7 +1051,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1055,7 +1059,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1075,20 +1079,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEDFC1B-B0AD-4EAF-96B8-DF2C11F9039A}">
   <dimension ref="A1:BA22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="23" width="9.140625" style="12"/>
-    <col min="47" max="47" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="23" width="9.1796875" style="12"/>
+    <col min="47" max="47" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="C2" s="12" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1257,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="3" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>33</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>9500</v>
       </c>
       <c r="AT3" s="11">
-        <f t="shared" ref="AT3:AX3" si="7">+AS3+500</f>
+        <f t="shared" ref="AT3" si="7">+AS3+500</f>
         <v>10000</v>
       </c>
       <c r="AU3" s="11">
@@ -1390,7 +1394,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="4" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>34</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>41.903999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:50" s="19" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50" s="19" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="19" t="s">
         <v>17</v>
       </c>
@@ -1554,75 +1558,75 @@
         <v>539.41800000000001</v>
       </c>
       <c r="AH5" s="19">
-        <f>+AH3+AH4</f>
+        <f t="shared" ref="AH5:AN5" si="9">+AH3+AH4</f>
         <v>2227.904</v>
       </c>
       <c r="AI5" s="19">
-        <f>+AI3+AI4</f>
+        <f t="shared" si="9"/>
         <v>3500</v>
       </c>
       <c r="AJ5" s="19">
-        <f>+AJ3+AJ4</f>
+        <f t="shared" si="9"/>
         <v>4500</v>
       </c>
       <c r="AK5" s="19">
-        <f>+AK3+AK4</f>
+        <f t="shared" si="9"/>
         <v>5500</v>
       </c>
       <c r="AL5" s="19">
-        <f>+AL3+AL4</f>
+        <f t="shared" si="9"/>
         <v>6000</v>
       </c>
       <c r="AM5" s="19">
-        <f>+AM3+AM4</f>
+        <f t="shared" si="9"/>
         <v>6500</v>
       </c>
       <c r="AN5" s="19">
-        <f>+AN3+AN4</f>
+        <f t="shared" si="9"/>
         <v>7000</v>
       </c>
       <c r="AO5" s="19">
-        <f t="shared" ref="AO5:AS5" si="9">+AO3+AO4</f>
+        <f t="shared" ref="AO5:AS5" si="10">+AO3+AO4</f>
         <v>7500</v>
       </c>
       <c r="AP5" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8000</v>
       </c>
       <c r="AQ5" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8500</v>
       </c>
       <c r="AR5" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9000</v>
       </c>
       <c r="AS5" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9500</v>
       </c>
       <c r="AT5" s="19">
-        <f t="shared" ref="AT5" si="10">+AT3+AT4</f>
+        <f t="shared" ref="AT5" si="11">+AT3+AT4</f>
         <v>10000</v>
       </c>
       <c r="AU5" s="19">
-        <f t="shared" ref="AU5" si="11">+AU3+AU4</f>
+        <f t="shared" ref="AU5" si="12">+AU3+AU4</f>
         <v>5000</v>
       </c>
       <c r="AV5" s="19">
-        <f t="shared" ref="AV5" si="12">+AV3+AV4</f>
+        <f t="shared" ref="AV5" si="13">+AV3+AV4</f>
         <v>4000</v>
       </c>
       <c r="AW5" s="19">
-        <f t="shared" ref="AW5" si="13">+AW3+AW4</f>
+        <f t="shared" ref="AW5" si="14">+AW3+AW4</f>
         <v>3200</v>
       </c>
       <c r="AX5" s="19">
-        <f t="shared" ref="AX5" si="14">+AX3+AX4</f>
+        <f t="shared" ref="AX5" si="15">+AX3+AX4</f>
         <v>2560</v>
       </c>
     </row>
-    <row r="6" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>37</v>
       </c>
@@ -1690,67 +1694,67 @@
         <v>350</v>
       </c>
       <c r="AJ6" s="11">
-        <f t="shared" ref="AJ6:AS6" si="15">+AJ5*0.1</f>
+        <f t="shared" ref="AJ6:AS6" si="16">+AJ5*0.1</f>
         <v>450</v>
       </c>
       <c r="AK6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>550</v>
       </c>
       <c r="AL6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>600</v>
       </c>
       <c r="AM6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>650</v>
       </c>
       <c r="AN6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>700</v>
       </c>
       <c r="AO6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>750</v>
       </c>
       <c r="AP6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>800</v>
       </c>
       <c r="AQ6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>850</v>
       </c>
       <c r="AR6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>900</v>
       </c>
       <c r="AS6" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>950</v>
       </c>
       <c r="AT6" s="11">
-        <f t="shared" ref="AT6" si="16">+AT5*0.1</f>
+        <f t="shared" ref="AT6" si="17">+AT5*0.1</f>
         <v>1000</v>
       </c>
       <c r="AU6" s="11">
-        <f t="shared" ref="AU6" si="17">+AU5*0.1</f>
+        <f t="shared" ref="AU6" si="18">+AU5*0.1</f>
         <v>500</v>
       </c>
       <c r="AV6" s="11">
-        <f t="shared" ref="AV6" si="18">+AV5*0.1</f>
+        <f t="shared" ref="AV6" si="19">+AV5*0.1</f>
         <v>400</v>
       </c>
       <c r="AW6" s="11">
-        <f t="shared" ref="AW6" si="19">+AW5*0.1</f>
+        <f t="shared" ref="AW6" si="20">+AW5*0.1</f>
         <v>320</v>
       </c>
       <c r="AX6" s="11">
-        <f t="shared" ref="AX6" si="20">+AX5*0.1</f>
+        <f t="shared" ref="AX6" si="21">+AX5*0.1</f>
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>38</v>
       </c>
@@ -1759,31 +1763,31 @@
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="18">
-        <f t="shared" ref="G7:M7" si="21">+G5-G6</f>
+        <f t="shared" ref="G7:M7" si="22">+G5-G6</f>
         <v>178.56700000000001</v>
       </c>
       <c r="H7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>320.06200000000001</v>
       </c>
       <c r="I7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.1050000000000004</v>
       </c>
       <c r="J7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>33.683999999999969</v>
       </c>
       <c r="K7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30.108000000000001</v>
       </c>
       <c r="L7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>80.172999999999988</v>
       </c>
       <c r="M7" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>136.22499999999999</v>
       </c>
       <c r="N7" s="18">
@@ -1795,27 +1799,27 @@
         <v>211.523</v>
       </c>
       <c r="P7" s="18">
-        <f t="shared" ref="P7:U7" si="22">+P5-P6</f>
+        <f t="shared" ref="P7:U7" si="23">+P5-P6</f>
         <v>257.01099999999997</v>
       </c>
       <c r="Q7" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>303.83999999999997</v>
       </c>
       <c r="R7" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>378.363</v>
       </c>
       <c r="S7" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>369.41700000000003</v>
       </c>
       <c r="T7" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>437.04500000000002</v>
       </c>
       <c r="U7" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>529.80899999999997</v>
       </c>
       <c r="V7" s="18"/>
@@ -1833,67 +1837,67 @@
         <v>3150</v>
       </c>
       <c r="AJ7" s="11">
-        <f t="shared" ref="AJ7:AS7" si="23">+AJ5-AJ6</f>
+        <f t="shared" ref="AJ7:AS7" si="24">+AJ5-AJ6</f>
         <v>4050</v>
       </c>
       <c r="AK7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4950</v>
       </c>
       <c r="AL7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5400</v>
       </c>
       <c r="AM7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5850</v>
       </c>
       <c r="AN7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6300</v>
       </c>
       <c r="AO7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6750</v>
       </c>
       <c r="AP7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7200</v>
       </c>
       <c r="AQ7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7650</v>
       </c>
       <c r="AR7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8100</v>
       </c>
       <c r="AS7" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8550</v>
       </c>
       <c r="AT7" s="11">
-        <f t="shared" ref="AT7" si="24">+AT5-AT6</f>
+        <f t="shared" ref="AT7" si="25">+AT5-AT6</f>
         <v>9000</v>
       </c>
       <c r="AU7" s="11">
-        <f t="shared" ref="AU7" si="25">+AU5-AU6</f>
+        <f t="shared" ref="AU7" si="26">+AU5-AU6</f>
         <v>4500</v>
       </c>
       <c r="AV7" s="11">
-        <f t="shared" ref="AV7" si="26">+AV5-AV6</f>
+        <f t="shared" ref="AV7" si="27">+AV5-AV6</f>
         <v>3600</v>
       </c>
       <c r="AW7" s="11">
-        <f t="shared" ref="AW7" si="27">+AW5-AW6</f>
+        <f t="shared" ref="AW7" si="28">+AW5-AW6</f>
         <v>2880</v>
       </c>
       <c r="AX7" s="11">
-        <f t="shared" ref="AX7" si="28">+AX5-AX6</f>
+        <f t="shared" ref="AX7" si="29">+AX5-AX6</f>
         <v>2304</v>
       </c>
     </row>
-    <row r="8" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
@@ -1953,11 +1957,11 @@
         <v>370.88499999999999</v>
       </c>
       <c r="AE8" s="11">
-        <f t="shared" ref="AE8:AE9" si="29">SUM(G8:J8)</f>
+        <f t="shared" ref="AE8:AE9" si="30">SUM(G8:J8)</f>
         <v>580.52</v>
       </c>
     </row>
-    <row r="9" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>40</v>
       </c>
@@ -2017,7 +2021,7 @@
         <v>171.643</v>
       </c>
       <c r="AE9" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>307.64400000000001</v>
       </c>
       <c r="AI9" s="11">
@@ -2025,67 +2029,67 @@
         <v>350</v>
       </c>
       <c r="AJ9" s="11">
-        <f t="shared" ref="AJ9:AS9" si="30">+AJ5*0.1</f>
+        <f t="shared" ref="AJ9:AS9" si="31">+AJ5*0.1</f>
         <v>450</v>
       </c>
       <c r="AK9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>550</v>
       </c>
       <c r="AL9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>600</v>
       </c>
       <c r="AM9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>650</v>
       </c>
       <c r="AN9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>700</v>
       </c>
       <c r="AO9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>750</v>
       </c>
       <c r="AP9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>800</v>
       </c>
       <c r="AQ9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>850</v>
       </c>
       <c r="AR9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>900</v>
       </c>
       <c r="AS9" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>950</v>
       </c>
       <c r="AT9" s="11">
-        <f t="shared" ref="AT9:AX9" si="31">+AT5*0.1</f>
+        <f t="shared" ref="AT9:AX9" si="32">+AT5*0.1</f>
         <v>1000</v>
       </c>
       <c r="AU9" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>500</v>
       </c>
       <c r="AV9" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>400</v>
       </c>
       <c r="AW9" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>320</v>
       </c>
       <c r="AX9" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>36</v>
       </c>
@@ -2094,63 +2098,63 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="18">
-        <f t="shared" ref="G10:U10" si="32">+G8+G9</f>
+        <f t="shared" ref="G10:U10" si="33">+G8+G9</f>
         <v>178.58100000000002</v>
       </c>
       <c r="H10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>224.92500000000001</v>
       </c>
       <c r="I10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>220.06299999999999</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>264.59499999999997</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>252.834</v>
       </c>
       <c r="L10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>254.71699999999998</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>344.86200000000002</v>
       </c>
       <c r="N10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>283.08500000000004</v>
       </c>
       <c r="O10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>315.02699999999999</v>
       </c>
       <c r="P10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>357.48599999999999</v>
       </c>
       <c r="Q10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>383.685</v>
       </c>
       <c r="R10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>515.19899999999996</v>
       </c>
       <c r="S10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>460.964</v>
       </c>
       <c r="T10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>480.98500000000001</v>
       </c>
       <c r="U10" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>513.63799999999992</v>
       </c>
       <c r="V10" s="18"/>
@@ -2168,67 +2172,67 @@
         <v>350</v>
       </c>
       <c r="AJ10" s="11">
-        <f t="shared" ref="AJ10:AS10" si="33">+AJ9+AJ8</f>
+        <f t="shared" ref="AJ10:AS10" si="34">+AJ9+AJ8</f>
         <v>450</v>
       </c>
       <c r="AK10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>550</v>
       </c>
       <c r="AL10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>600</v>
       </c>
       <c r="AM10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>650</v>
       </c>
       <c r="AN10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>700</v>
       </c>
       <c r="AO10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>750</v>
       </c>
       <c r="AP10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>800</v>
       </c>
       <c r="AQ10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>850</v>
       </c>
       <c r="AR10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>900</v>
       </c>
       <c r="AS10" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>950</v>
       </c>
       <c r="AT10" s="11">
-        <f t="shared" ref="AT10" si="34">+AT9+AT8</f>
+        <f t="shared" ref="AT10" si="35">+AT9+AT8</f>
         <v>1000</v>
       </c>
       <c r="AU10" s="11">
-        <f t="shared" ref="AU10" si="35">+AU9+AU8</f>
+        <f t="shared" ref="AU10" si="36">+AU9+AU8</f>
         <v>500</v>
       </c>
       <c r="AV10" s="11">
-        <f t="shared" ref="AV10" si="36">+AV9+AV8</f>
+        <f t="shared" ref="AV10" si="37">+AV9+AV8</f>
         <v>400</v>
       </c>
       <c r="AW10" s="11">
-        <f t="shared" ref="AW10" si="37">+AW9+AW8</f>
+        <f t="shared" ref="AW10" si="38">+AW9+AW8</f>
         <v>320</v>
       </c>
       <c r="AX10" s="11">
-        <f t="shared" ref="AX10" si="38">+AX9+AX8</f>
+        <f t="shared" ref="AX10" si="39">+AX9+AX8</f>
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
@@ -2237,63 +2241,63 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18">
-        <f t="shared" ref="G11:U11" si="39">+G7-G10</f>
+        <f t="shared" ref="G11:U11" si="40">+G7-G10</f>
         <v>-1.4000000000010004E-2</v>
       </c>
       <c r="H11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>95.137</v>
       </c>
       <c r="I11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-212.958</v>
       </c>
       <c r="J11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-230.911</v>
       </c>
       <c r="K11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-222.726</v>
       </c>
       <c r="L11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-174.54399999999998</v>
       </c>
       <c r="M11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-208.63700000000003</v>
       </c>
       <c r="N11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-113.75500000000005</v>
       </c>
       <c r="O11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-103.50399999999999</v>
       </c>
       <c r="P11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-100.47500000000002</v>
       </c>
       <c r="Q11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-79.845000000000027</v>
       </c>
       <c r="R11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-136.83599999999996</v>
       </c>
       <c r="S11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-91.546999999999969</v>
       </c>
       <c r="T11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-43.94</v>
       </c>
       <c r="U11" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16.171000000000049</v>
       </c>
       <c r="V11" s="18"/>
@@ -2311,67 +2315,67 @@
         <v>2800</v>
       </c>
       <c r="AJ11" s="11">
-        <f t="shared" ref="AJ11:AS11" si="40">+AJ7-AJ10</f>
+        <f t="shared" ref="AJ11:AS11" si="41">+AJ7-AJ10</f>
         <v>3600</v>
       </c>
       <c r="AK11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4400</v>
       </c>
       <c r="AL11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4800</v>
       </c>
       <c r="AM11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5200</v>
       </c>
       <c r="AN11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5600</v>
       </c>
       <c r="AO11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6000</v>
       </c>
       <c r="AP11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6400</v>
       </c>
       <c r="AQ11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6800</v>
       </c>
       <c r="AR11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7200</v>
       </c>
       <c r="AS11" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7600</v>
       </c>
       <c r="AT11" s="11">
-        <f t="shared" ref="AT11" si="41">+AT7-AT10</f>
+        <f t="shared" ref="AT11" si="42">+AT7-AT10</f>
         <v>8000</v>
       </c>
       <c r="AU11" s="11">
-        <f t="shared" ref="AU11" si="42">+AU7-AU10</f>
+        <f t="shared" ref="AU11" si="43">+AU7-AU10</f>
         <v>4000</v>
       </c>
       <c r="AV11" s="11">
-        <f t="shared" ref="AV11" si="43">+AV7-AV10</f>
+        <f t="shared" ref="AV11" si="44">+AV7-AV10</f>
         <v>3200</v>
       </c>
       <c r="AW11" s="11">
-        <f t="shared" ref="AW11" si="44">+AW7-AW10</f>
+        <f t="shared" ref="AW11" si="45">+AW7-AW10</f>
         <v>2560</v>
       </c>
       <c r="AX11" s="11">
-        <f t="shared" ref="AX11" si="45">+AX7-AX10</f>
+        <f t="shared" ref="AX11" si="46">+AX7-AX10</f>
         <v>2048</v>
       </c>
     </row>
-    <row r="12" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>45</v>
       </c>
@@ -2441,7 +2445,7 @@
         <v>-1.5009999999999999</v>
       </c>
       <c r="AE12" s="11">
-        <f t="shared" ref="AE12:AE14" si="46">SUM(G12:J12)</f>
+        <f t="shared" ref="AE12:AE14" si="47">SUM(G12:J12)</f>
         <v>-0.94399999999999995</v>
       </c>
       <c r="AI12" s="11">
@@ -2449,67 +2453,67 @@
         <v>67.48</v>
       </c>
       <c r="AJ12" s="11">
-        <f t="shared" ref="AJ12:AX12" si="47">+AI19*$BA$19</f>
+        <f t="shared" ref="AJ12:AX12" si="48">+AI19*$BA$19</f>
         <v>116.22716000000001</v>
       </c>
       <c r="AK12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>179.40302172</v>
       </c>
       <c r="AL12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>257.25287308923998</v>
       </c>
       <c r="AM12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>343.22617193175705</v>
       </c>
       <c r="AN12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>437.46101685459689</v>
       </c>
       <c r="AO12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>540.09785414112503</v>
       </c>
       <c r="AP12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>651.27951766152421</v>
       </c>
       <c r="AQ12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>771.1512694617702</v>
       </c>
       <c r="AR12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>899.86084104262034</v>
       </c>
       <c r="AS12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1037.558475340345</v>
       </c>
       <c r="AT12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1184.3969694211307</v>
       </c>
       <c r="AU12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1340.5317179012902</v>
       </c>
       <c r="AV12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1431.3207571056121</v>
       </c>
       <c r="AW12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1510.0532099764075</v>
       </c>
       <c r="AX12" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1579.2441145460064</v>
       </c>
     </row>
-    <row r="13" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>44</v>
       </c>
@@ -2518,63 +2522,63 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18">
-        <f t="shared" ref="G13:U13" si="48">+G11+G12</f>
+        <f t="shared" ref="G13:U13" si="49">+G11+G12</f>
         <v>-0.43400000000000993</v>
       </c>
       <c r="H13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>94.811999999999998</v>
       </c>
       <c r="I13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-213.25299999999999</v>
       </c>
       <c r="J13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-230.815</v>
       </c>
       <c r="K13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-222.858</v>
       </c>
       <c r="L13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-170.80999999999997</v>
       </c>
       <c r="M13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-201.41500000000002</v>
       </c>
       <c r="N13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-100.82000000000005</v>
       </c>
       <c r="O13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-87.103999999999985</v>
       </c>
       <c r="P13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-80.03400000000002</v>
       </c>
       <c r="Q13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-49.796000000000028</v>
       </c>
       <c r="R13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-96.807999999999964</v>
       </c>
       <c r="S13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-53.163999999999966</v>
       </c>
       <c r="T13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-5.0069999999999979</v>
       </c>
       <c r="U13" s="18">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>56.757000000000048</v>
       </c>
       <c r="V13" s="18"/>
@@ -2592,67 +2596,67 @@
         <v>2867.48</v>
       </c>
       <c r="AJ13" s="11">
-        <f t="shared" ref="AJ13:AS13" si="49">+AJ11+AJ12</f>
+        <f t="shared" ref="AJ13:AS13" si="50">+AJ11+AJ12</f>
         <v>3716.2271599999999</v>
       </c>
       <c r="AK13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>4579.4030217199997</v>
       </c>
       <c r="AL13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5057.25287308924</v>
       </c>
       <c r="AM13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5543.2261719317567</v>
       </c>
       <c r="AN13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>6037.4610168545969</v>
       </c>
       <c r="AO13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>6540.097854141125</v>
       </c>
       <c r="AP13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>7051.2795176615246</v>
       </c>
       <c r="AQ13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>7571.1512694617704</v>
       </c>
       <c r="AR13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8099.8608410426205</v>
       </c>
       <c r="AS13" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8637.5584753403455</v>
       </c>
       <c r="AT13" s="11">
-        <f t="shared" ref="AT13" si="50">+AT11+AT12</f>
+        <f t="shared" ref="AT13" si="51">+AT11+AT12</f>
         <v>9184.3969694211301</v>
       </c>
       <c r="AU13" s="11">
-        <f t="shared" ref="AU13" si="51">+AU11+AU12</f>
+        <f t="shared" ref="AU13" si="52">+AU11+AU12</f>
         <v>5340.53171790129</v>
       </c>
       <c r="AV13" s="11">
-        <f t="shared" ref="AV13" si="52">+AV11+AV12</f>
+        <f t="shared" ref="AV13" si="53">+AV11+AV12</f>
         <v>4631.3207571056118</v>
       </c>
       <c r="AW13" s="11">
-        <f t="shared" ref="AW13" si="53">+AW11+AW12</f>
+        <f t="shared" ref="AW13" si="54">+AW11+AW12</f>
         <v>4070.0532099764077</v>
       </c>
       <c r="AX13" s="11">
-        <f t="shared" ref="AX13" si="54">+AX11+AX12</f>
+        <f t="shared" ref="AX13" si="55">+AX11+AX12</f>
         <v>3627.2441145460061</v>
       </c>
     </row>
-    <row r="14" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>43</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>3.1030000000000002</v>
       </c>
       <c r="AE14" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.5220000000000002</v>
       </c>
       <c r="AI14" s="11">
@@ -2720,67 +2724,67 @@
         <v>430.12200000000001</v>
       </c>
       <c r="AJ14" s="11">
-        <f t="shared" ref="AJ14:AS14" si="55">+AJ13*0.15</f>
+        <f t="shared" ref="AJ14:AS14" si="56">+AJ13*0.15</f>
         <v>557.43407400000001</v>
       </c>
       <c r="AK14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>686.91045325799996</v>
       </c>
       <c r="AL14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>758.58793096338593</v>
       </c>
       <c r="AM14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>831.48392578976348</v>
       </c>
       <c r="AN14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>905.61915252818949</v>
       </c>
       <c r="AO14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>981.01467812116869</v>
       </c>
       <c r="AP14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>1057.6919276492285</v>
       </c>
       <c r="AQ14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>1135.6726904192656</v>
       </c>
       <c r="AR14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>1214.979126156393</v>
       </c>
       <c r="AS14" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>1295.6337713010519</v>
       </c>
       <c r="AT14" s="11">
-        <f t="shared" ref="AT14" si="56">+AT13*0.15</f>
+        <f t="shared" ref="AT14" si="57">+AT13*0.15</f>
         <v>1377.6595454131696</v>
       </c>
       <c r="AU14" s="11">
-        <f t="shared" ref="AU14" si="57">+AU13*0.15</f>
+        <f t="shared" ref="AU14" si="58">+AU13*0.15</f>
         <v>801.0797576851935</v>
       </c>
       <c r="AV14" s="11">
-        <f t="shared" ref="AV14" si="58">+AV13*0.15</f>
+        <f t="shared" ref="AV14" si="59">+AV13*0.15</f>
         <v>694.69811356584171</v>
       </c>
       <c r="AW14" s="11">
-        <f t="shared" ref="AW14" si="59">+AW13*0.15</f>
+        <f t="shared" ref="AW14" si="60">+AW13*0.15</f>
         <v>610.50798149646118</v>
       </c>
       <c r="AX14" s="11">
-        <f t="shared" ref="AX14" si="60">+AX13*0.15</f>
+        <f t="shared" ref="AX14" si="61">+AX13*0.15</f>
         <v>544.08661718190092</v>
       </c>
     </row>
-    <row r="15" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>42</v>
       </c>
@@ -2789,63 +2793,63 @@
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18">
-        <f t="shared" ref="G15:U15" si="61">+G13-G14</f>
+        <f t="shared" ref="G15:U15" si="62">+G13-G14</f>
         <v>-11.618000000000009</v>
       </c>
       <c r="H15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>93.161000000000001</v>
       </c>
       <c r="I15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-210.50399999999999</v>
       </c>
       <c r="J15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-229.251</v>
       </c>
       <c r="K15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-219.97300000000001</v>
       </c>
       <c r="L15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-162.58099999999996</v>
       </c>
       <c r="M15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-195.43300000000002</v>
       </c>
       <c r="N15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-98.19500000000005</v>
       </c>
       <c r="O15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-39.796999999999983</v>
       </c>
       <c r="P15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-35.965000000000018</v>
       </c>
       <c r="Q15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-39.159000000000027</v>
       </c>
       <c r="R15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-134.80199999999996</v>
       </c>
       <c r="S15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-40.410999999999966</v>
       </c>
       <c r="T15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-15.513999999999998</v>
       </c>
       <c r="U15" s="18">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>60.14300000000005</v>
       </c>
       <c r="V15" s="18"/>
@@ -2863,128 +2867,128 @@
         <v>2437.3580000000002</v>
       </c>
       <c r="AJ15" s="11">
-        <f t="shared" ref="AJ15:AS15" si="62">+AJ13-AJ14</f>
+        <f t="shared" ref="AJ15:AS15" si="63">+AJ13-AJ14</f>
         <v>3158.7930859999997</v>
       </c>
       <c r="AK15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3892.4925684619998</v>
       </c>
       <c r="AL15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4298.6649421258544</v>
       </c>
       <c r="AM15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4711.7422461419928</v>
       </c>
       <c r="AN15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5131.8418643264076</v>
       </c>
       <c r="AO15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5559.0831760199562</v>
       </c>
       <c r="AP15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5993.5875900122955</v>
       </c>
       <c r="AQ15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>6435.4785790425049</v>
       </c>
       <c r="AR15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>6884.8817148862272</v>
       </c>
       <c r="AS15" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>7341.9247040392938</v>
       </c>
       <c r="AT15" s="11">
-        <f t="shared" ref="AT15" si="63">+AT13-AT14</f>
+        <f t="shared" ref="AT15" si="64">+AT13-AT14</f>
         <v>7806.7374240079607</v>
       </c>
       <c r="AU15" s="11">
-        <f t="shared" ref="AU15" si="64">+AU13-AU14</f>
+        <f t="shared" ref="AU15" si="65">+AU13-AU14</f>
         <v>4539.4519602160963</v>
       </c>
       <c r="AV15" s="11">
-        <f t="shared" ref="AV15" si="65">+AV13-AV14</f>
+        <f t="shared" ref="AV15" si="66">+AV13-AV14</f>
         <v>3936.6226435397703</v>
       </c>
       <c r="AW15" s="11">
-        <f t="shared" ref="AW15" si="66">+AW13-AW14</f>
+        <f t="shared" ref="AW15" si="67">+AW13-AW14</f>
         <v>3459.5452284799467</v>
       </c>
       <c r="AX15" s="11">
-        <f t="shared" ref="AX15" si="67">+AX13-AX14</f>
+        <f t="shared" ref="AX15" si="68">+AX13-AX14</f>
         <v>3083.1574973641054</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>41</v>
       </c>
       <c r="G16" s="16">
-        <f t="shared" ref="G16:O16" si="68">+G15/G17</f>
+        <f t="shared" ref="G16:O16" si="69">+G15/G17</f>
         <v>-0.23260882165652619</v>
       </c>
       <c r="H16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.8147777385731643</v>
       </c>
       <c r="I16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-4.0901030441563018</v>
       </c>
       <c r="J16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-4.4884442106047544</v>
       </c>
       <c r="K16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-4.2234003755639771</v>
       </c>
       <c r="L16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-2.9666799440804881</v>
       </c>
       <c r="M16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-3.5402184873447244</v>
       </c>
       <c r="N16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.7736214881680428</v>
       </c>
       <c r="O16" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-0.71635076516528962</v>
       </c>
       <c r="P16" s="16">
-        <f t="shared" ref="P16:U16" si="69">+P15/P17</f>
+        <f t="shared" ref="P16:U16" si="70">+P15/P17</f>
         <v>-0.64420803242602753</v>
       </c>
       <c r="Q16" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.67366575550301044</v>
       </c>
       <c r="R16" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-2.2801873250969602</v>
       </c>
       <c r="S16" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.68135226311598418</v>
       </c>
       <c r="T16" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.26078140928768095</v>
       </c>
       <c r="U16" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1.0009236863215716</v>
       </c>
       <c r="AD16" s="1">
@@ -2996,7 +3000,7 @@
         <v>-7.0298407971513539</v>
       </c>
     </row>
-    <row r="17" spans="2:53" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:53" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>1</v>
       </c>
@@ -3059,7 +3063,7 @@
         <v>50.955919249999994</v>
       </c>
     </row>
-    <row r="18" spans="2:53" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:53" x14ac:dyDescent="0.25">
       <c r="AZ18" t="s">
         <v>68</v>
       </c>
@@ -3067,7 +3071,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="2:53" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>3</v>
       </c>
@@ -3079,63 +3083,63 @@
         <v>5811.3580000000002</v>
       </c>
       <c r="AJ19" s="11">
-        <f t="shared" ref="AJ19:AX19" si="70">+AI19+AJ15</f>
+        <f t="shared" ref="AJ19:AX19" si="71">+AI19+AJ15</f>
         <v>8970.1510859999999</v>
       </c>
       <c r="AK19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>12862.643654461999</v>
       </c>
       <c r="AL19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>17161.308596587853</v>
       </c>
       <c r="AM19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>21873.050842729845</v>
       </c>
       <c r="AN19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>27004.892707056253</v>
       </c>
       <c r="AO19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>32563.975883076208</v>
       </c>
       <c r="AP19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>38557.563473088507</v>
       </c>
       <c r="AQ19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>44993.042052131015</v>
       </c>
       <c r="AR19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>51877.923767017244</v>
       </c>
       <c r="AS19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>59219.848471056539</v>
       </c>
       <c r="AT19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>67026.585895064505</v>
       </c>
       <c r="AU19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>71566.037855280607</v>
       </c>
       <c r="AV19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>75502.660498820376</v>
       </c>
       <c r="AW19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>78962.205727300316</v>
       </c>
       <c r="AX19" s="11">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>82045.363224664427</v>
       </c>
       <c r="AZ19" t="s">
@@ -3145,31 +3149,31 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="20" spans="2:53" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:53" x14ac:dyDescent="0.25">
       <c r="AZ20" t="s">
         <v>69</v>
       </c>
       <c r="BA20" s="11">
         <f>NPV(BA18,AI15:AX15)+Main!K5-Main!K6</f>
-        <v>45168.399374084111</v>
-      </c>
-    </row>
-    <row r="21" spans="2:53" x14ac:dyDescent="0.2">
+        <v>46981.399374084111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:53" x14ac:dyDescent="0.25">
       <c r="AZ21" t="s">
         <v>75</v>
       </c>
       <c r="BA21" s="1">
         <f>BA20/Main!K3</f>
-        <v>751.55406612452759</v>
-      </c>
-    </row>
-    <row r="22" spans="2:53" x14ac:dyDescent="0.2">
+        <v>729.41737052907661</v>
+      </c>
+    </row>
+    <row r="22" spans="2:53" x14ac:dyDescent="0.25">
       <c r="AZ22" t="s">
         <v>77</v>
       </c>
       <c r="BA22" s="22">
         <f>+BA21/541-1</f>
-        <v>0.38919420725421006</v>
+        <v>0.34827610079311766</v>
       </c>
     </row>
   </sheetData>
@@ -3184,18 +3188,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2FDDFC-CAB0-4107-91CA-8EC6E676B90E}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>54</v>
       </c>
@@ -3203,7 +3207,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>56</v>
       </c>
@@ -3211,7 +3215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -3219,7 +3223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -3227,7 +3231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -3235,37 +3239,37 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C9" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C16" s="21" t="s">
         <v>65</v>
       </c>
